--- a/output/pdf_financials_xlsx/IAN.xlsx
+++ b/output/pdf_financials_xlsx/IAN.xlsx
@@ -1126,13 +1126,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>13.104</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>18.543</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="35">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>13.104</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>18.543</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>11.65</v>
       </c>
     </row>
     <row r="37">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/IAN.xlsx
+++ b/output/pdf_financials_xlsx/IAN.xlsx
@@ -480,20 +480,14 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>63.169</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>75.114</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>65.697</v>
       </c>
     </row>
     <row r="5">
@@ -502,20 +496,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -524,20 +512,14 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>63.169</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>75.114</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>65.697</v>
       </c>
     </row>
     <row r="7">
@@ -546,20 +528,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>67.863</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>62.182</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>60.886</v>
       </c>
     </row>
     <row r="8">
@@ -568,20 +544,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -590,20 +560,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -612,20 +576,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>92.904</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>83.627</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>81.114</v>
       </c>
     </row>
     <row r="11">
@@ -634,20 +592,14 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-29.735</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-8.513</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-15.417</v>
       </c>
     </row>
     <row r="12">
@@ -656,20 +608,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -678,20 +624,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -700,20 +640,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -722,20 +656,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>5.156</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>13.751</v>
       </c>
     </row>
     <row r="16">
@@ -744,20 +672,14 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-49.458</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-25.314</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-23.165</v>
       </c>
     </row>
     <row r="17">
@@ -766,20 +688,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-27.163</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>17.678</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-17.038</v>
       </c>
     </row>
     <row r="18">
@@ -832,20 +748,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-76.621</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-7.636</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-40.203</v>
       </c>
     </row>
     <row r="21">
@@ -854,20 +764,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -876,20 +780,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -898,20 +796,14 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-76.621</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-7.636</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-40.203</v>
       </c>
     </row>
     <row r="24">
@@ -920,20 +812,14 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="25">
@@ -942,20 +828,14 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="26">
@@ -986,20 +866,14 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-49.458</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-25.314</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>-23.165</v>
       </c>
     </row>
     <row r="28">
@@ -1008,20 +882,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>25.143</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>22.681</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>17.215</v>
       </c>
     </row>
     <row r="29">
@@ -1030,20 +898,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-24.315</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-2.633</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-5.95</v>
       </c>
     </row>
     <row r="30">
@@ -1052,20 +914,14 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>-38.49198182652884</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-3.505338552067524</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-9.056730139884623</v>
       </c>
     </row>
     <row r="31">
@@ -1074,20 +930,14 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-54.92134740587974</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-69.83487398277633</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-73.55061515216921</v>
       </c>
     </row>
     <row r="32">
@@ -1096,20 +946,14 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>-121.2952555842265</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-10.16588119391858</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-61.19457509475319</v>
       </c>
     </row>
     <row r="33">
@@ -2168,20 +2012,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-76.621</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-7.636</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-40.203</v>
       </c>
     </row>
     <row r="100">
@@ -2190,20 +2028,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>24.736</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>19.29</v>
       </c>
     </row>
     <row r="101">
@@ -2212,20 +2044,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2234,20 +2060,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2256,20 +2076,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2278,20 +2092,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2300,20 +2108,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2322,20 +2124,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -2344,20 +2140,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>4.535</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>1.845</v>
       </c>
     </row>
     <row r="108">
@@ -2366,20 +2156,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2388,20 +2172,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2410,20 +2188,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>4.624</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>4.889</v>
       </c>
     </row>
     <row r="111">
@@ -2432,20 +2204,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>-3.572</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>-5.519</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>-23.777</v>
       </c>
     </row>
     <row r="112">
@@ -2454,20 +2220,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2476,20 +2236,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2498,20 +2252,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2520,20 +2268,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2542,20 +2284,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>-2.504</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>-0.136</v>
       </c>
     </row>
     <row r="117">
@@ -2564,20 +2300,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2586,20 +2316,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2608,20 +2332,14 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>-6.281</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>2.297</v>
       </c>
     </row>
     <row r="120">
@@ -2630,20 +2348,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2652,20 +2364,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2674,20 +2380,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2696,20 +2396,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2718,20 +2412,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>-0.056</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2740,20 +2428,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>-0.056</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2762,20 +2444,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2806,20 +2482,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2828,20 +2498,14 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>-0.618</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>-0.339</v>
+      </c>
+      <c r="D129" s="3" t="n">
+        <v>-12.672</v>
       </c>
     </row>
     <row r="130">
@@ -2872,20 +2536,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2894,20 +2552,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-5.008</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-10.375</v>
       </c>
     </row>
     <row r="133">
@@ -2938,20 +2590,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-3.572</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>-5.519</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>-23.777</v>
       </c>
     </row>
     <row r="135">
@@ -2960,20 +2606,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-3.572</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-5.519</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-23.777</v>
       </c>
     </row>
   </sheetData>
@@ -2987,7 +2627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4059,6 +3699,2498 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>-76.621</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-7.636</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>-40.203</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>-1.086</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>15.745</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>17.173</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>16.602</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Accretion expense</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>4.624</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>4.889</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>27.17</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>24.736</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>19.29</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Write-downs, (recoveries) and other charges, net (Refer to Note 17)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>-1.236</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>3.013</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Gains from deconsolidation of subsidiaries</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>-12.085</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Inventory reserve</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" s="5" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>-0.111</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>4.535</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>1.845</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Losses from changes in fair value of financial instruments</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="5" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.008</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Loss on debt extinguishment</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Loss on equity method investments</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" s="5" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.013</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Remeasurement of contingent consideration</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Deferred income taxes</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>DeferredIncomeTax</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>-3.431</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>-20.274</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Loss on sale of promissory note</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>1.409</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Change in operating assets and liabilities (Refer to Note 17)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" s="5" t="n">
+        <v>29.664</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-5.604</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>9.282</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>NET CASH FLOW PROVIDED BY OPERATING ACTIVITIES $</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>3.777</v>
+      </c>
+      <c r="F54" s="5" t="n">
+        <v>12.544</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>3.146</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Purchase of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>-3.572</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>-5.519</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-23.777</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Acquisition of other intangible assets</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-2.504</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.205</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.136</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Investments in associates</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" s="5" t="n">
+        <v>-0.76</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-0.385</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" s="5" t="n">
+        <v>2.514</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Cash impact from acquisitions</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-0.675</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-1.425</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of subsidiaries</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>15.814</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Proceeds from sale of promissory notes</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>10.104</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Proceeds from notes receivables</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>1.715</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NET CASH PROVIDED BY (USED IN) INVESTING ACTIVITIES $</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>-6.281</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>2.297</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Repayments of debt and professional fee obligations</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>-0.056</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>-12.365</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Taxes paid related to net share settlement of restricted stock units</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>-0.569</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-0.283</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>-0.307</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>NET CASH USED IN FINANCING ACTIVITIES $</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>-0.618</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>-0.339</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>-12.672</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CASH AND RESTRICTED CASH</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>THE PERIOD</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>-1.231</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>5.924</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>-7.229</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>CASH AND RESTRICTED CASH</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2(f))</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>19.099</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>CASH AND RESTRICTED CASH</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CASH AND RESTRICTED CASH, END OF PERIOD (Refer to Note 2(f)) $</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>19.099</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>(Recoveries), write-downs and other charges, net (Refer to Note 17)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="F70" s="5" t="n">
+        <v>-1.236</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>(Gain)/loss from deconsolidation of subsidiaries</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" s="5" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM OPERATING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Loss on debt extinguishment (Refer to Note 9)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0.114</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Cash impact of deconsolidation of subsidiaries</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>-0.068</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>NET CASH USED IN INVESTING ACTIVITIES $</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>-4.39</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>-6.281</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>CASH FLOW FROM FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Repayment of debt</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-0.056</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CASH AND RESTRICTED CASH</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CASH AND RESTRICTED CASH, BEGINNING OF PERIOD (Refer to Note 2(f))</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>14.406</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>13.175</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Revenues, net of discounts $</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>167.567</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>143.986</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Costs and expenses applicable to revenues (exclusive of depreciation and amortization expense shown separately below)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-92.453</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>-78.289</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>75.114</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>65.697</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Selling, general and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>67.863</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>62.182</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>60.886</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Depreciation and amortization</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>DepreciationAndAmortization</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="n">
+        <v>25.143</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>22.681</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>17.215</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Write-downs, (recoveries) and other charges, net</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-1.236</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>3.013</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>92.904</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>83.627</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>81.114</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Loss from operations</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="n">
+        <v>-29.735</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-8.513</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-15.417</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Interest and other income</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="n">
+        <v>1.334</v>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>5.156</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>13.751</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E86" s="5" t="n">
+        <v>-15.745</v>
+      </c>
+      <c r="F86" s="5" t="n">
+        <v>-17.173</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>-16.602</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Accretion expense</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>-3.95</v>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-4.624</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-4.889</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Loss on debt extinguishment</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.114</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Losses from changes in fair value of financial instruments</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>-0.074</v>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.008</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="n">
+        <v>-49.458</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-25.314</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-23.165</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Income tax expense (benefit)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>-17.678</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>17.038</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>-76.621</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-7.636</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-40.203</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Net loss per share - basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding - basic and diluted</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>6437.45</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>6539.803</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>6702.331</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Year Ended December</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>2.025</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Balance – January 1, 2025 6,678,395 $ 1,269,738 $</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>-65.542</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>-1335.28</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Share-based compensation 99,085 1,845</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>1.845</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Net loss — —</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>-40.203</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-40.203</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Balance – December 31, 2025 6,859,128 $ 1,272,443 $</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>-103.04</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-1375.483</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Year Ended December</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>2.024</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.031</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Balance – January 1, 2024 6,510,527 $ 1,265,978 $</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>-61.666</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>-1327.644</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Share-based compensation 110,269 2,107</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital         Accumulated Deficit           (Deficit)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Balance – December 31, 2024 6,678,395 $ 1,269,738 $</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>-65.542</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>-1335.28</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>(Adjusted)</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Revenues, net of discounts $</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" s="5" t="n">
+        <v>159.237</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>167.567</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>(Adjusted)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Costs and expenses applicable to revenues (exclusive of depreciation and amortization expense shown separately below)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>-96.068</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>-92.453</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>(Adjusted)</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GrossProfit</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>63.169</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>75.114</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>(Recoveries), write-downs and other charges, net</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" s="5" t="n">
+        <v>-0.102</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>-1.236</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Loss on debt extinguishment (Refer to Note 9)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" s="5" t="n">
+        <v>-1.288</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>-0.114</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Income tax (benefit) expense</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" s="5" t="n">
+        <v>27.163</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>-17.678</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital                Deficit                 (Deficit)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Balance – January 1, 2024 6,510,527 $ 1,265,978 $</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>-61.666</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>-1327.644</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Shares ('000)             Capital                Deficit                 (Deficit)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Share-based compensation 110,269 2,107</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>2.107</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Share settlement for taxes paid related to restricted</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Share settlement for taxes paid related to restricted</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>-0.283</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Shares issued for legal settlements (Refer to Note</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Shares issued for legal settlements (Refer to Note</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>10(a))</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Shares issued for 2024 NJ Amendment (Refer to Note</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>10(a))</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Net loss — —</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="n">
+        <v>-7.636</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>-7.636</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>10(a))</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Balance – December 31, 2024 6,678,395 $ 1,269,738 $</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>-65.542</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>-1335.28</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>10(a))</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Year Ended December</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" s="5" t="n">
+        <v>2.023</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>('000)                Capital                  Deficit           Equity (Deficit)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Balance – January 1, 2023 6,403,289 $ 1,262,012 $</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>10.989</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>-1251.023</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>('000)                Capital                  Deficit           Equity (Deficit)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Share-based compensation 141,604 4,535</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>4.535</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>stock units</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Net loss — —</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>-76.621</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>-76.621</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>stock units</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Balance – December 31, 2023 6,510,527 $ 1,265,978 $</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" s="5" t="n">
+        <v>-61.666</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>-1327.644</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
